--- a/content/W03/D1/briefs/C2_W03_D01_challenges_log_STUDENT.xlsx
+++ b/content/W03/D1/briefs/C2_W03_D01_challenges_log_STUDENT.xlsx
@@ -636,7 +636,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="100"/>
   </cols>
@@ -693,7 +693,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L64"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
@@ -1988,7 +1988,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60"/>
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
         <v>28</v>
       </c>
@@ -2084,7 +2084,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
@@ -2147,7 +2147,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="n">
         <v>1</v>
       </c>

--- a/content/W03/D1/briefs/C2_W03_D01_challenges_log_STUDENT.xlsx
+++ b/content/W03/D1/briefs/C2_W03_D01_challenges_log_STUDENT.xlsx
@@ -2124,7 +2124,7 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>Nobody in the group had worked in diagnostics, so we could not say what 'home collection' means in the files or who pays for it.</t>
+          <t>Nobody in the group had worked in diagnostics, so we could not say what 'at-home' means in the files or who pays for it.</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>Wrote a one-line definition into our vocabulary map and agreed that a home-collection booking is still one booking, counted once.</t>
+          <t>Wrote a one-line definition into our vocabulary map and agreed that an at-home booking is still one booking, counted once.</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">

--- a/content/W03/D1/briefs/C2_W03_D01_challenges_log_STUDENT.xlsx
+++ b/content/W03/D1/briefs/C2_W03_D01_challenges_log_STUDENT.xlsx
@@ -528,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>How to use this log</t>
+          <t>How do you fill this log?</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Challenges log</t>
+          <t>Where did the group get stuck, and what did it decide?</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Where the group stands</t>
+          <t>How many challenges are still open, and which one goes to the checkpoint?</t>
         </is>
       </c>
     </row>
@@ -2030,14 +2030,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Entry one, as another group might write it</t>
+          <t>What does a good entry one look like?</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Copy the shape, not the words. Your entry one is about your own first stop.</t>
+          <t>Another group's entry one. Copy its shape; your entry is about your own first stop.</t>
         </is>
       </c>
     </row>
